--- a/data/material.xlsx
+++ b/data/material.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="52">
   <si>
     <t>Metal</t>
   </si>
@@ -201,9 +201,6 @@
     <t>Cd</t>
   </si>
   <si>
-    <t>Cu</t>
-  </si>
-  <si>
     <t>Pt</t>
   </si>
   <si>
@@ -277,6 +274,9 @@
   </si>
   <si>
     <t>Pr</t>
+  </si>
+  <si>
+    <t>Cu</t>
   </si>
   <si>
     <t>Pd</t>
@@ -1372,7 +1372,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K152"/>
+  <dimension ref="A1:K151"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.4"/>
   <cols>
     <col min="1" max="2" width="9.0625" style="8"/>
@@ -1856,25 +1856,25 @@
         <v>2</v>
       </c>
       <c r="E14" s="8">
-        <v>3.509</v>
+        <v>3.333</v>
       </c>
       <c r="F14" s="8">
         <v>1</v>
       </c>
       <c r="G14" s="8">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="H14" s="8">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="I14" s="8">
         <v>0</v>
       </c>
       <c r="J14" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K14" s="15">
-        <v>1.706986</v>
+        <v>1.602375</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1882,34 +1882,34 @@
         <v>25</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C15" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D15" s="8">
         <v>2</v>
       </c>
       <c r="E15" s="8">
-        <v>3.333</v>
+        <v>2.41</v>
       </c>
       <c r="F15" s="8">
         <v>1</v>
       </c>
       <c r="G15" s="8">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="H15" s="8">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="I15" s="8">
         <v>0</v>
       </c>
       <c r="J15" s="8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>1.602375</v>
+        <v>1.169628</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1926,25 +1926,25 @@
         <v>2</v>
       </c>
       <c r="E16" s="8">
-        <v>2.41</v>
+        <v>6.612</v>
       </c>
       <c r="F16" s="8">
         <v>1</v>
       </c>
       <c r="G16" s="8">
-        <v>0.83</v>
+        <v>1.54</v>
       </c>
       <c r="H16" s="8">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="I16" s="8">
         <v>0</v>
       </c>
       <c r="J16" s="8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K16" s="15">
-        <v>1.169628</v>
+        <v>1.027571</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1952,109 +1952,109 @@
         <v>27</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C17" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D17" s="8">
         <v>2</v>
       </c>
       <c r="E17" s="8">
-        <v>6.612</v>
+        <v>2.899</v>
       </c>
       <c r="F17" s="8">
         <v>1</v>
       </c>
       <c r="G17" s="8">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="H17" s="8">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="I17" s="8">
         <v>0</v>
       </c>
       <c r="J17" s="8">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K17" s="15">
-        <v>1.027571</v>
+        <v>2.131648</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="8" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C18" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D18" s="8">
         <v>2</v>
       </c>
       <c r="E18" s="8">
-        <v>2.899</v>
+        <v>2.703</v>
       </c>
       <c r="F18" s="8">
         <v>1</v>
       </c>
       <c r="G18" s="8">
-        <v>1.91</v>
+        <v>0.74</v>
       </c>
       <c r="H18" s="8">
-        <v>0.69</v>
+        <v>0.74</v>
       </c>
       <c r="I18" s="8">
         <v>0</v>
       </c>
       <c r="J18" s="8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K18" s="15">
-        <v>2.131648</v>
+        <v>1.118473</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="8" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C19" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D19" s="8">
         <v>2</v>
       </c>
       <c r="E19" s="8">
-        <v>2.703</v>
+        <v>3.046</v>
       </c>
       <c r="F19" s="8">
         <v>1</v>
       </c>
       <c r="G19" s="8">
-        <v>0.74</v>
+        <v>0.985</v>
       </c>
       <c r="H19" s="8">
-        <v>0.74</v>
+        <v>0.985</v>
       </c>
       <c r="I19" s="8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J19" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K19" s="15">
-        <v>1.118473</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>2.556934</v>
+      </c>
+    </row>
+    <row r="20" ht="13.5" customHeight="1" spans="1:11">
       <c r="A20" s="8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>12</v>
@@ -2066,30 +2066,30 @@
         <v>2</v>
       </c>
       <c r="E20" s="8">
-        <v>3.046</v>
+        <v>2.41</v>
       </c>
       <c r="F20" s="8">
         <v>1</v>
       </c>
       <c r="G20" s="8">
-        <v>0.985</v>
+        <v>1.55</v>
       </c>
       <c r="H20" s="8">
-        <v>0.985</v>
+        <v>0.83</v>
       </c>
       <c r="I20" s="8">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J20" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K20" s="15">
-        <v>2.556934</v>
-      </c>
-    </row>
-    <row r="21" ht="13.5" customHeight="1" spans="1:11">
+        <v>2.156795</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>12</v>
@@ -2101,25 +2101,25 @@
         <v>2</v>
       </c>
       <c r="E21" s="8">
-        <v>2.41</v>
+        <v>4.412</v>
       </c>
       <c r="F21" s="8">
         <v>1</v>
       </c>
       <c r="G21" s="8">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="H21" s="8">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="I21" s="8">
         <v>0</v>
       </c>
       <c r="J21" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K21" s="15">
-        <v>2.156795</v>
+        <v>2.136792</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2127,22 +2127,22 @@
         <v>30</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C22" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D22" s="8">
         <v>2</v>
       </c>
       <c r="E22" s="8">
-        <v>4.412</v>
+        <v>2.941</v>
       </c>
       <c r="F22" s="8">
         <v>1</v>
       </c>
       <c r="G22" s="8">
-        <v>2.2</v>
+        <v>0.68</v>
       </c>
       <c r="H22" s="8">
         <v>0.68</v>
@@ -2154,7 +2154,7 @@
         <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>2.136792</v>
+        <v>1.489393</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2162,34 +2162,34 @@
         <v>31</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C23" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D23" s="8">
         <v>2</v>
       </c>
       <c r="E23" s="8">
-        <v>2.941</v>
+        <v>3.071</v>
       </c>
       <c r="F23" s="8">
         <v>1</v>
       </c>
       <c r="G23" s="8">
-        <v>0.68</v>
+        <v>0.977</v>
       </c>
       <c r="H23" s="8">
-        <v>0.68</v>
+        <v>0.977</v>
       </c>
       <c r="I23" s="8">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J23" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K23" s="15">
-        <v>1.489393</v>
+        <v>2.580205</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2206,25 +2206,25 @@
         <v>2</v>
       </c>
       <c r="E24" s="8">
-        <v>3.071</v>
+        <v>2.778</v>
       </c>
       <c r="F24" s="8">
         <v>1</v>
       </c>
       <c r="G24" s="8">
-        <v>0.977</v>
+        <v>1.31</v>
       </c>
       <c r="H24" s="8">
-        <v>0.977</v>
+        <v>0.72</v>
       </c>
       <c r="I24" s="8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J24" s="8">
         <v>0</v>
       </c>
       <c r="K24" s="15">
-        <v>2.580205</v>
+        <v>2.168522</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2241,16 +2241,16 @@
         <v>2</v>
       </c>
       <c r="E25" s="8">
-        <v>2.778</v>
+        <v>2</v>
       </c>
       <c r="F25" s="8">
         <v>1</v>
       </c>
       <c r="G25" s="8">
-        <v>1.31</v>
+        <v>1</v>
       </c>
       <c r="H25" s="8">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="I25" s="8">
         <v>0</v>
@@ -2259,10 +2259,10 @@
         <v>0</v>
       </c>
       <c r="K25" s="15">
-        <v>2.168522</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>2.163146</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" spans="1:11">
       <c r="A26" s="8" t="s">
         <v>34</v>
       </c>
@@ -2276,25 +2276,25 @@
         <v>2</v>
       </c>
       <c r="E26" s="8">
-        <v>2</v>
+        <v>4.878</v>
       </c>
       <c r="F26" s="8">
         <v>1</v>
       </c>
       <c r="G26" s="8">
-        <v>1</v>
+        <v>1.66</v>
       </c>
       <c r="H26" s="8">
-        <v>1</v>
+        <v>0.615</v>
       </c>
       <c r="I26" s="8">
         <v>0</v>
       </c>
       <c r="J26" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K26" s="15">
-        <v>2.163146</v>
+        <v>2.142304</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" spans="1:11">
@@ -2311,30 +2311,30 @@
         <v>2</v>
       </c>
       <c r="E27" s="8">
-        <v>4.878</v>
+        <v>2.625</v>
       </c>
       <c r="F27" s="8">
         <v>1</v>
       </c>
       <c r="G27" s="8">
-        <v>1.66</v>
+        <v>1.12</v>
       </c>
       <c r="H27" s="8">
-        <v>0.615</v>
+        <v>0.97</v>
       </c>
       <c r="I27" s="8">
         <v>0</v>
       </c>
       <c r="J27" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K27" s="15">
-        <v>2.142304</v>
+        <v>2.534345</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" spans="1:11">
       <c r="A28" s="8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>12</v>
@@ -2346,30 +2346,30 @@
         <v>2</v>
       </c>
       <c r="E28" s="8">
-        <v>2.625</v>
+        <v>4.412</v>
       </c>
       <c r="F28" s="8">
         <v>1</v>
       </c>
       <c r="G28" s="8">
-        <v>1.12</v>
+        <v>2.2</v>
       </c>
       <c r="H28" s="8">
-        <v>0.97</v>
+        <v>0.68</v>
       </c>
       <c r="I28" s="8">
         <v>0</v>
       </c>
       <c r="J28" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K28" s="15">
-        <v>2.534345</v>
+        <v>2.125508</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" spans="1:11">
       <c r="A29" s="8" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>12</v>
@@ -2381,25 +2381,25 @@
         <v>2</v>
       </c>
       <c r="E29" s="8">
-        <v>4.412</v>
+        <v>6.757</v>
       </c>
       <c r="F29" s="8">
         <v>1</v>
       </c>
       <c r="G29" s="8">
-        <v>2.2</v>
+        <v>0.74</v>
       </c>
       <c r="H29" s="8">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="I29" s="8">
         <v>0</v>
       </c>
       <c r="J29" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K29" s="15">
-        <v>2.125508</v>
+        <v>2.532645</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" spans="1:11">
@@ -2416,100 +2416,100 @@
         <v>2</v>
       </c>
       <c r="E30" s="8">
-        <v>6.757</v>
+        <v>2.956</v>
       </c>
       <c r="F30" s="8">
         <v>1</v>
       </c>
       <c r="G30" s="8">
-        <v>0.74</v>
+        <v>1.015</v>
       </c>
       <c r="H30" s="8">
-        <v>0.74</v>
+        <v>1.015</v>
       </c>
       <c r="I30" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J30" s="8">
         <v>0</v>
       </c>
       <c r="K30" s="15">
-        <v>2.532645</v>
+        <v>2.530767</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" spans="1:11">
       <c r="A31" s="8" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="B31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="8">
+        <v>3.04</v>
+      </c>
+      <c r="D31" s="8">
+        <v>3</v>
+      </c>
+      <c r="E31" s="8">
+        <v>2.679</v>
+      </c>
+      <c r="F31" s="8">
+        <v>1</v>
+      </c>
+      <c r="G31" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="H31" s="8">
+        <v>1.12</v>
+      </c>
+      <c r="I31" s="8">
+        <v>6</v>
+      </c>
+      <c r="J31" s="8">
+        <v>0</v>
+      </c>
+      <c r="K31" s="15">
+        <v>1.799442</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C32" s="8">
         <v>3.44</v>
       </c>
-      <c r="D31" s="8">
-        <v>2</v>
-      </c>
-      <c r="E31" s="8">
-        <v>2.956</v>
-      </c>
-      <c r="F31" s="8">
-        <v>1</v>
-      </c>
-      <c r="G31" s="8">
-        <v>1.015</v>
-      </c>
-      <c r="H31" s="8">
-        <v>1.015</v>
-      </c>
-      <c r="I31" s="8">
-        <v>10</v>
-      </c>
-      <c r="J31" s="8">
-        <v>0</v>
-      </c>
-      <c r="K31" s="15">
-        <v>2.530767</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:11">
-      <c r="A32" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" s="8">
-        <v>3.04</v>
-      </c>
       <c r="D32" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" s="8">
-        <v>2.679</v>
+        <v>6.612</v>
       </c>
       <c r="F32" s="8">
         <v>1</v>
       </c>
       <c r="G32" s="8">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="H32" s="8">
-        <v>1.12</v>
+        <v>0.605</v>
       </c>
       <c r="I32" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J32" s="8">
         <v>0</v>
       </c>
       <c r="K32" s="15">
-        <v>1.799442</v>
+        <v>2.068608</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="8" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>12</v>
@@ -2521,25 +2521,25 @@
         <v>2</v>
       </c>
       <c r="E33" s="8">
-        <v>6.612</v>
+        <v>5.66</v>
       </c>
       <c r="F33" s="8">
         <v>1</v>
       </c>
       <c r="G33" s="8">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="H33" s="8">
-        <v>0.605</v>
+        <v>0.53</v>
       </c>
       <c r="I33" s="8">
         <v>0</v>
       </c>
       <c r="J33" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" s="15">
-        <v>2.068608</v>
+        <v>1.82443</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2547,112 +2547,112 @@
         <v>39</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C34" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D34" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="8">
-        <v>5.66</v>
+        <v>5.556</v>
       </c>
       <c r="F34" s="8">
         <v>1</v>
       </c>
       <c r="G34" s="8">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="H34" s="8">
-        <v>0.53</v>
+        <v>0.72</v>
       </c>
       <c r="I34" s="8">
         <v>0</v>
       </c>
       <c r="J34" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" s="15">
-        <v>1.82443</v>
+        <v>1.126688</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="8" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C35" s="8">
         <v>3.04</v>
       </c>
       <c r="D35" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" s="8">
-        <v>5.556</v>
+        <v>2.814</v>
       </c>
       <c r="F35" s="8">
         <v>1</v>
       </c>
       <c r="G35" s="8">
-        <v>1.33</v>
+        <v>1.066</v>
       </c>
       <c r="H35" s="8">
-        <v>0.72</v>
+        <v>1.066</v>
       </c>
       <c r="I35" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J35" s="8">
         <v>0</v>
       </c>
       <c r="K35" s="15">
-        <v>1.126688</v>
+        <v>1.510422</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="8" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C36" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D36" s="8">
         <v>2</v>
       </c>
       <c r="E36" s="8">
-        <v>2.814</v>
+        <v>5.556</v>
       </c>
       <c r="F36" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="8">
-        <v>1.066</v>
+        <v>0.72</v>
       </c>
       <c r="H36" s="8">
-        <v>1.066</v>
+        <v>0.72</v>
       </c>
       <c r="I36" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J36" s="8">
         <v>0</v>
       </c>
       <c r="K36" s="15">
-        <v>1.510422</v>
+        <v>0.835874</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="8" t="s">
         <v>40</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="C37" s="8">
         <v>3.44</v>
@@ -2661,135 +2661,135 @@
         <v>2</v>
       </c>
       <c r="E37" s="8">
-        <v>5.556</v>
+        <v>2.74</v>
       </c>
       <c r="F37" s="8">
         <v>0</v>
       </c>
       <c r="G37" s="8">
-        <v>0.72</v>
+        <v>1.2</v>
       </c>
       <c r="H37" s="8">
-        <v>0.72</v>
+        <v>1.095</v>
       </c>
       <c r="I37" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J37" s="8">
         <v>0</v>
       </c>
       <c r="K37" s="15">
-        <v>0.835874</v>
+        <v>2.00169</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="8" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C38" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D38" s="8">
         <v>2</v>
       </c>
       <c r="E38" s="8">
-        <v>2.74</v>
+        <v>5.556</v>
       </c>
       <c r="F38" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="8">
-        <v>1.2</v>
+        <v>0.72</v>
       </c>
       <c r="H38" s="8">
-        <v>1.095</v>
+        <v>0.72</v>
       </c>
       <c r="I38" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J38" s="8">
         <v>0</v>
       </c>
       <c r="K38" s="15">
-        <v>2.00169</v>
+        <v>1.200858</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>16</v>
-      </c>
       <c r="C39" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D39" s="8">
         <v>2</v>
       </c>
       <c r="E39" s="8">
-        <v>5.556</v>
+        <v>2.74</v>
       </c>
       <c r="F39" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="8">
-        <v>0.72</v>
+        <v>1.2</v>
       </c>
       <c r="H39" s="8">
-        <v>0.72</v>
+        <v>1.095</v>
       </c>
       <c r="I39" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J39" s="8">
         <v>0</v>
       </c>
       <c r="K39" s="15">
-        <v>1.200858</v>
+        <v>2.103654</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="8" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C40" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D40" s="8">
         <v>2</v>
       </c>
       <c r="E40" s="8">
-        <v>2.74</v>
+        <v>4.412</v>
       </c>
       <c r="F40" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" s="8">
-        <v>1.2</v>
+        <v>0.68</v>
       </c>
       <c r="H40" s="8">
-        <v>1.095</v>
+        <v>0.68</v>
       </c>
       <c r="I40" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J40" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K40" s="15">
-        <v>2.103654</v>
+        <v>1.585818</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="8" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>16</v>
@@ -2801,30 +2801,30 @@
         <v>2</v>
       </c>
       <c r="E41" s="8">
-        <v>4.412</v>
+        <v>2.105</v>
       </c>
       <c r="F41" s="8">
         <v>1</v>
       </c>
       <c r="G41" s="8">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="H41" s="8">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="I41" s="8">
         <v>0</v>
       </c>
       <c r="J41" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K41" s="15">
-        <v>1.585818</v>
+        <v>1.54896</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>16</v>
@@ -2836,16 +2836,16 @@
         <v>2</v>
       </c>
       <c r="E42" s="8">
-        <v>2.105</v>
+        <v>2.703</v>
       </c>
       <c r="F42" s="8">
         <v>1</v>
       </c>
       <c r="G42" s="8">
-        <v>0.95</v>
+        <v>0.74</v>
       </c>
       <c r="H42" s="8">
-        <v>0.95</v>
+        <v>0.74</v>
       </c>
       <c r="I42" s="8">
         <v>0</v>
@@ -2854,12 +2854,12 @@
         <v>10</v>
       </c>
       <c r="K42" s="15">
-        <v>1.54896</v>
+        <v>1.528249</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>16</v>
@@ -2871,30 +2871,30 @@
         <v>2</v>
       </c>
       <c r="E43" s="8">
-        <v>2.703</v>
+        <v>2.814</v>
       </c>
       <c r="F43" s="8">
         <v>1</v>
       </c>
       <c r="G43" s="8">
-        <v>0.74</v>
+        <v>1.2</v>
       </c>
       <c r="H43" s="8">
-        <v>0.74</v>
+        <v>1.066</v>
       </c>
       <c r="I43" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J43" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K43" s="15">
-        <v>1.528249</v>
+        <v>1.787093</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>16</v>
@@ -2906,30 +2906,30 @@
         <v>2</v>
       </c>
       <c r="E44" s="8">
-        <v>2.814</v>
+        <v>3.333</v>
       </c>
       <c r="F44" s="8">
         <v>1</v>
       </c>
       <c r="G44" s="8">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="H44" s="8">
-        <v>1.066</v>
+        <v>0.6</v>
       </c>
       <c r="I44" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J44" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K44" s="15">
-        <v>1.787093</v>
+        <v>1.104241</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>16</v>
@@ -2941,30 +2941,30 @@
         <v>2</v>
       </c>
       <c r="E45" s="8">
-        <v>3.333</v>
+        <v>3.279</v>
       </c>
       <c r="F45" s="8">
         <v>1</v>
       </c>
       <c r="G45" s="8">
-        <v>0.6</v>
+        <v>1.83</v>
       </c>
       <c r="H45" s="8">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="I45" s="8">
         <v>0</v>
       </c>
       <c r="J45" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K45" s="15">
-        <v>1.104241</v>
+        <v>1.56898</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>16</v>
@@ -2976,30 +2976,30 @@
         <v>2</v>
       </c>
       <c r="E46" s="8">
-        <v>3.279</v>
+        <v>2.899</v>
       </c>
       <c r="F46" s="8">
         <v>1</v>
       </c>
       <c r="G46" s="8">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="H46" s="8">
-        <v>0.61</v>
+        <v>0.69</v>
       </c>
       <c r="I46" s="8">
         <v>0</v>
       </c>
       <c r="J46" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K46" s="15">
-        <v>1.56898</v>
+        <v>1.54663</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>16</v>
@@ -3011,30 +3011,30 @@
         <v>2</v>
       </c>
       <c r="E47" s="8">
-        <v>2.899</v>
+        <v>4.878</v>
       </c>
       <c r="F47" s="8">
         <v>1</v>
       </c>
       <c r="G47" s="8">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="H47" s="8">
-        <v>0.69</v>
+        <v>0.615</v>
       </c>
       <c r="I47" s="8">
         <v>0</v>
       </c>
       <c r="J47" s="8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K47" s="15">
-        <v>1.54663</v>
+        <v>1.514437</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="8" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>16</v>
@@ -3046,30 +3046,30 @@
         <v>2</v>
       </c>
       <c r="E48" s="8">
-        <v>4.878</v>
+        <v>3.046</v>
       </c>
       <c r="F48" s="8">
         <v>1</v>
       </c>
       <c r="G48" s="8">
-        <v>1.66</v>
+        <v>0.985</v>
       </c>
       <c r="H48" s="8">
-        <v>0.615</v>
+        <v>0.985</v>
       </c>
       <c r="I48" s="8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J48" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K48" s="15">
-        <v>1.514437</v>
+        <v>1.792761</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="8" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>16</v>
@@ -3081,33 +3081,33 @@
         <v>2</v>
       </c>
       <c r="E49" s="8">
-        <v>3.046</v>
+        <v>4.511</v>
       </c>
       <c r="F49" s="8">
         <v>1</v>
       </c>
       <c r="G49" s="8">
-        <v>0.985</v>
+        <v>0.665</v>
       </c>
       <c r="H49" s="8">
-        <v>0.985</v>
+        <v>0.665</v>
       </c>
       <c r="I49" s="8">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J49" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K49" s="15">
-        <v>1.792761</v>
+        <v>1.410876</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="8" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C50" s="8">
         <v>3.04</v>
@@ -3116,33 +3116,33 @@
         <v>2</v>
       </c>
       <c r="E50" s="8">
-        <v>4.511</v>
+        <v>2.105</v>
       </c>
       <c r="F50" s="8">
         <v>1</v>
       </c>
       <c r="G50" s="8">
-        <v>0.665</v>
+        <v>0.95</v>
       </c>
       <c r="H50" s="8">
-        <v>0.665</v>
+        <v>0.95</v>
       </c>
       <c r="I50" s="8">
         <v>0</v>
       </c>
       <c r="J50" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K50" s="15">
-        <v>1.410876</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="8" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C51" s="8">
         <v>3.04</v>
@@ -3151,30 +3151,30 @@
         <v>2</v>
       </c>
       <c r="E51" s="8">
-        <v>2.105</v>
+        <v>2.532</v>
       </c>
       <c r="F51" s="8">
         <v>1</v>
       </c>
       <c r="G51" s="8">
-        <v>0.95</v>
+        <v>1.63</v>
       </c>
       <c r="H51" s="8">
-        <v>0.95</v>
+        <v>0.79</v>
       </c>
       <c r="I51" s="8">
         <v>0</v>
       </c>
       <c r="J51" s="8">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K51" s="15">
-        <v>1.4</v>
+        <v>1.490735</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>16</v>
@@ -3186,30 +3186,30 @@
         <v>2</v>
       </c>
       <c r="E52" s="8">
-        <v>2.532</v>
+        <v>3.75</v>
       </c>
       <c r="F52" s="8">
         <v>1</v>
       </c>
       <c r="G52" s="8">
-        <v>1.63</v>
+        <v>0.8</v>
       </c>
       <c r="H52" s="8">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I52" s="8">
         <v>0</v>
       </c>
       <c r="J52" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K52" s="15">
-        <v>1.490735</v>
+        <v>1.487745</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="8" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>16</v>
@@ -3221,68 +3221,68 @@
         <v>2</v>
       </c>
       <c r="E53" s="8">
-        <v>3.75</v>
+        <v>1.786</v>
       </c>
       <c r="F53" s="8">
         <v>1</v>
       </c>
       <c r="G53" s="8">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H53" s="8">
-        <v>0.8</v>
+        <v>1.12</v>
       </c>
       <c r="I53" s="8">
         <v>0</v>
       </c>
       <c r="J53" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K53" s="15">
-        <v>1.487745</v>
+        <v>1.875867</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C54" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D54" s="8">
         <v>2</v>
       </c>
       <c r="E54" s="8">
-        <v>1.786</v>
+        <v>2.58</v>
       </c>
       <c r="F54" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" s="8">
-        <v>1</v>
+        <v>1.163</v>
       </c>
       <c r="H54" s="8">
-        <v>1.12</v>
+        <v>1.163</v>
       </c>
       <c r="I54" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J54" s="8">
         <v>0</v>
       </c>
       <c r="K54" s="15">
-        <v>1.875867</v>
+        <v>2.064318</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="8" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C55" s="8">
         <v>3.44</v>
@@ -3291,103 +3291,103 @@
         <v>2</v>
       </c>
       <c r="E55" s="8">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="F55" s="8">
         <v>0</v>
       </c>
       <c r="G55" s="8">
-        <v>1.163</v>
+        <v>1</v>
       </c>
       <c r="H55" s="8">
-        <v>1.163</v>
+        <v>1</v>
       </c>
       <c r="I55" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J55" s="8">
         <v>0</v>
       </c>
       <c r="K55" s="15">
-        <v>2.064318</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
+        <v>1.444555</v>
+      </c>
+    </row>
+    <row r="56" s="3" customFormat="1" spans="1:11">
       <c r="A56" s="8" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C56" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D56" s="8">
         <v>2</v>
       </c>
       <c r="E56" s="8">
-        <v>2</v>
+        <v>3.077</v>
       </c>
       <c r="F56" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" s="8">
-        <v>1</v>
+        <v>1.88</v>
       </c>
       <c r="H56" s="8">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="I56" s="8">
         <v>0</v>
       </c>
       <c r="J56" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K56" s="15">
-        <v>1.444555</v>
+        <v>1.420009</v>
       </c>
     </row>
     <row r="57" s="3" customFormat="1" spans="1:11">
       <c r="A57" s="8" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C57" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D57" s="8">
         <v>2</v>
       </c>
       <c r="E57" s="8">
-        <v>3.077</v>
+        <v>2.778</v>
       </c>
       <c r="F57" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="8">
-        <v>1.88</v>
+        <v>1.31</v>
       </c>
       <c r="H57" s="8">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="I57" s="8">
         <v>0</v>
       </c>
       <c r="J57" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K57" s="15">
-        <v>1.420009</v>
+        <v>1.431071</v>
       </c>
     </row>
     <row r="58" s="3" customFormat="1" spans="1:11">
       <c r="A58" s="8" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C58" s="8">
         <v>3.44</v>
@@ -3396,33 +3396,33 @@
         <v>2</v>
       </c>
       <c r="E58" s="8">
-        <v>2.778</v>
+        <v>3.333</v>
       </c>
       <c r="F58" s="8">
         <v>0</v>
       </c>
       <c r="G58" s="8">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="H58" s="8">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="I58" s="8">
         <v>0</v>
       </c>
       <c r="J58" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K58" s="15">
-        <v>1.431071</v>
+        <v>1.001426</v>
       </c>
     </row>
     <row r="59" s="3" customFormat="1" spans="1:11">
       <c r="A59" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C59" s="8">
         <v>3.44</v>
@@ -3431,103 +3431,103 @@
         <v>2</v>
       </c>
       <c r="E59" s="8">
-        <v>3.333</v>
+        <v>2.685</v>
       </c>
       <c r="F59" s="8">
         <v>0</v>
       </c>
       <c r="G59" s="8">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="H59" s="8">
-        <v>0.6</v>
+        <v>0.745</v>
       </c>
       <c r="I59" s="8">
         <v>0</v>
       </c>
       <c r="J59" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K59" s="15">
-        <v>1.001426</v>
+        <v>1.442559</v>
       </c>
     </row>
     <row r="60" s="3" customFormat="1" spans="1:11">
       <c r="A60" s="8" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C60" s="8">
+        <v>3.04</v>
+      </c>
+      <c r="D60" s="8">
+        <v>2</v>
+      </c>
+      <c r="E60" s="8">
+        <v>2.625</v>
+      </c>
+      <c r="F60" s="8">
+        <v>1</v>
+      </c>
+      <c r="G60" s="8">
+        <v>1.143</v>
+      </c>
+      <c r="H60" s="8">
+        <v>1.143</v>
+      </c>
+      <c r="I60" s="8">
+        <v>1</v>
+      </c>
+      <c r="J60" s="8">
+        <v>0</v>
+      </c>
+      <c r="K60" s="15">
+        <v>1.836598</v>
+      </c>
+    </row>
+    <row r="61" s="4" customFormat="1" spans="1:11">
+      <c r="A61" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C61" s="8">
         <v>3.44</v>
       </c>
-      <c r="D60" s="8">
-        <v>2</v>
-      </c>
-      <c r="E60" s="8">
-        <v>2.685</v>
-      </c>
-      <c r="F60" s="8">
-        <v>0</v>
-      </c>
-      <c r="G60" s="8">
-        <v>1.88</v>
-      </c>
-      <c r="H60" s="8">
-        <v>0.745</v>
-      </c>
-      <c r="I60" s="8">
-        <v>0</v>
-      </c>
-      <c r="J60" s="8">
-        <v>7</v>
-      </c>
-      <c r="K60" s="15">
-        <v>1.442559</v>
-      </c>
-    </row>
-    <row r="61" s="3" customFormat="1" spans="1:11">
-      <c r="A61" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" s="8">
-        <v>3.04</v>
-      </c>
       <c r="D61" s="8">
         <v>2</v>
       </c>
       <c r="E61" s="8">
-        <v>2.625</v>
+        <v>2.907</v>
       </c>
       <c r="F61" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" s="8">
-        <v>1.143</v>
+        <v>1.27</v>
       </c>
       <c r="H61" s="8">
-        <v>1.143</v>
+        <v>1.032</v>
       </c>
       <c r="I61" s="8">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J61" s="8">
         <v>0</v>
       </c>
       <c r="K61" s="15">
-        <v>1.836598</v>
+        <v>2.030865</v>
       </c>
     </row>
     <row r="62" s="4" customFormat="1" spans="1:11">
       <c r="A62" s="8" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C62" s="8">
         <v>3.44</v>
@@ -3536,33 +3536,33 @@
         <v>2</v>
       </c>
       <c r="E62" s="8">
-        <v>2.907</v>
+        <v>2.65</v>
       </c>
       <c r="F62" s="8">
         <v>0</v>
       </c>
       <c r="G62" s="8">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="H62" s="8">
-        <v>1.032</v>
+        <v>1.132</v>
       </c>
       <c r="I62" s="8">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J62" s="8">
         <v>0</v>
       </c>
       <c r="K62" s="15">
-        <v>2.030865</v>
+        <v>2.014408</v>
       </c>
     </row>
     <row r="63" s="4" customFormat="1" spans="1:11">
       <c r="A63" s="8" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C63" s="8">
         <v>3.44</v>
@@ -3571,261 +3571,261 @@
         <v>2</v>
       </c>
       <c r="E63" s="8">
-        <v>2.65</v>
+        <v>2.899</v>
       </c>
       <c r="F63" s="8">
         <v>0</v>
       </c>
       <c r="G63" s="8">
-        <v>1.17</v>
+        <v>1.91</v>
       </c>
       <c r="H63" s="8">
-        <v>1.132</v>
+        <v>0.69</v>
       </c>
       <c r="I63" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J63" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K63" s="15">
-        <v>2.014408</v>
+        <v>1.421477</v>
       </c>
     </row>
     <row r="64" s="4" customFormat="1" spans="1:11">
       <c r="A64" s="8" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C64" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D64" s="8">
         <v>2</v>
       </c>
       <c r="E64" s="8">
-        <v>2.899</v>
+        <v>2.586</v>
       </c>
       <c r="F64" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" s="8">
-        <v>1.91</v>
+        <v>1.16</v>
       </c>
       <c r="H64" s="8">
-        <v>0.69</v>
+        <v>1.16</v>
       </c>
       <c r="I64" s="8">
         <v>0</v>
       </c>
       <c r="J64" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K64" s="15">
-        <v>1.421477</v>
+        <v>1.820521</v>
       </c>
     </row>
     <row r="65" s="4" customFormat="1" spans="1:11">
       <c r="A65" s="8" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C65" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D65" s="8">
         <v>2</v>
       </c>
       <c r="E65" s="8">
-        <v>2.586</v>
+        <v>2.508</v>
       </c>
       <c r="F65" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" s="8">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="H65" s="8">
-        <v>1.16</v>
+        <v>1.196</v>
       </c>
       <c r="I65" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" s="8">
         <v>0</v>
       </c>
       <c r="K65" s="15">
-        <v>1.820521</v>
+        <v>2.008039</v>
       </c>
     </row>
     <row r="66" s="4" customFormat="1" spans="1:11">
       <c r="A66" s="8" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C66" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D66" s="8">
         <v>2</v>
       </c>
       <c r="E66" s="8">
-        <v>2.508</v>
+        <v>2.988</v>
       </c>
       <c r="F66" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" s="8">
-        <v>1.12</v>
+        <v>1.004</v>
       </c>
       <c r="H66" s="8">
-        <v>1.196</v>
+        <v>1.004</v>
       </c>
       <c r="I66" s="8">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J66" s="8">
         <v>0</v>
       </c>
       <c r="K66" s="15">
-        <v>2.008039</v>
+        <v>1.816522</v>
       </c>
     </row>
     <row r="67" s="4" customFormat="1" spans="1:11">
       <c r="A67" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C67" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D67" s="8">
         <v>2</v>
       </c>
       <c r="E67" s="8">
-        <v>2.988</v>
+        <v>2.467</v>
       </c>
       <c r="F67" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" s="8">
-        <v>1.004</v>
+        <v>1.1</v>
       </c>
       <c r="H67" s="8">
-        <v>1.004</v>
+        <v>1.216</v>
       </c>
       <c r="I67" s="8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J67" s="8">
         <v>0</v>
       </c>
       <c r="K67" s="15">
-        <v>1.816522</v>
+        <v>2.01619</v>
       </c>
     </row>
     <row r="68" s="4" customFormat="1" spans="1:11">
       <c r="A68" s="8" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C68" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D68" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68" s="8">
-        <v>2.467</v>
+        <v>2.65</v>
       </c>
       <c r="F68" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" s="8">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="H68" s="8">
-        <v>1.216</v>
+        <v>1.132</v>
       </c>
       <c r="I68" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J68" s="8">
         <v>0</v>
       </c>
       <c r="K68" s="15">
-        <v>2.01619</v>
+        <v>1.881522</v>
       </c>
     </row>
     <row r="69" s="4" customFormat="1" spans="1:11">
       <c r="A69" s="8" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C69" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D69" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69" s="8">
-        <v>2.65</v>
+        <v>4.651</v>
       </c>
       <c r="F69" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" s="8">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="H69" s="8">
-        <v>1.132</v>
+        <v>0.645</v>
       </c>
       <c r="I69" s="8">
+        <v>0</v>
+      </c>
+      <c r="J69" s="8">
         <v>5</v>
       </c>
-      <c r="J69" s="8">
-        <v>0</v>
-      </c>
       <c r="K69" s="15">
-        <v>1.881522</v>
+        <v>1.414224</v>
       </c>
     </row>
     <row r="70" s="4" customFormat="1" spans="1:11">
       <c r="A70" s="8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C70" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D70" s="8">
         <v>2</v>
       </c>
       <c r="E70" s="8">
-        <v>4.651</v>
+        <v>2.985</v>
       </c>
       <c r="F70" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" s="8">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="H70" s="8">
-        <v>0.645</v>
+        <v>0.67</v>
       </c>
       <c r="I70" s="8">
         <v>0</v>
@@ -3834,82 +3834,82 @@
         <v>5</v>
       </c>
       <c r="K70" s="15">
-        <v>1.414224</v>
+        <v>1.284855</v>
       </c>
     </row>
     <row r="71" s="4" customFormat="1" spans="1:11">
       <c r="A71" s="8" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C71" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D71" s="8">
         <v>2</v>
       </c>
       <c r="E71" s="8">
-        <v>2.985</v>
+        <v>2.825</v>
       </c>
       <c r="F71" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" s="8">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="H71" s="8">
-        <v>0.67</v>
+        <v>1.062</v>
       </c>
       <c r="I71" s="8">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J71" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K71" s="15">
-        <v>1.284855</v>
+        <v>2.004851</v>
       </c>
     </row>
     <row r="72" s="4" customFormat="1" spans="1:11">
       <c r="A72" s="8" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C72" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D72" s="8">
         <v>2</v>
       </c>
       <c r="E72" s="8">
-        <v>2.825</v>
+        <v>2.78</v>
       </c>
       <c r="F72" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" s="8">
-        <v>1.24</v>
+        <v>1.079</v>
       </c>
       <c r="H72" s="8">
-        <v>1.062</v>
+        <v>1.079</v>
       </c>
       <c r="I72" s="8">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J72" s="8">
         <v>0</v>
       </c>
       <c r="K72" s="15">
-        <v>2.004851</v>
+        <v>1.778306</v>
       </c>
     </row>
     <row r="73" s="4" customFormat="1" spans="1:11">
       <c r="A73" s="8" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>16</v>
@@ -3921,208 +3921,208 @@
         <v>2</v>
       </c>
       <c r="E73" s="8">
-        <v>2.78</v>
+        <v>2.921</v>
       </c>
       <c r="F73" s="8">
         <v>1</v>
       </c>
       <c r="G73" s="8">
-        <v>1.079</v>
+        <v>1.027</v>
       </c>
       <c r="H73" s="8">
-        <v>1.079</v>
+        <v>1.027</v>
       </c>
       <c r="I73" s="8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J73" s="8">
         <v>0</v>
       </c>
       <c r="K73" s="15">
-        <v>1.778306</v>
-      </c>
-    </row>
-    <row r="74" s="4" customFormat="1" spans="1:11">
+        <v>1.772832</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
       <c r="A74" s="8" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C74" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D74" s="8">
         <v>2</v>
       </c>
       <c r="E74" s="8">
-        <v>2.921</v>
+        <v>4.412</v>
       </c>
       <c r="F74" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" s="8">
-        <v>1.027</v>
+        <v>0.68</v>
       </c>
       <c r="H74" s="8">
-        <v>1.027</v>
+        <v>0.68</v>
       </c>
       <c r="I74" s="8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J74" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K74" s="15">
-        <v>1.772832</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11">
+        <v>1.376217</v>
+      </c>
+    </row>
+    <row r="75" s="4" customFormat="1" spans="1:11">
       <c r="A75" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C75" s="8">
+        <v>3.04</v>
+      </c>
+      <c r="D75" s="8">
+        <v>3</v>
+      </c>
+      <c r="E75" s="8">
+        <v>2.703</v>
+      </c>
+      <c r="F75" s="8">
+        <v>1</v>
+      </c>
+      <c r="G75" s="8">
+        <v>1.65</v>
+      </c>
+      <c r="H75" s="8">
+        <v>0.74</v>
+      </c>
+      <c r="I75" s="8">
+        <v>0</v>
+      </c>
+      <c r="J75" s="8">
+        <v>10</v>
+      </c>
+      <c r="K75" s="15">
+        <v>1.189663</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B75" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C75" s="8">
+      <c r="B76" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C76" s="8">
         <v>3.44</v>
       </c>
-      <c r="D75" s="8">
-        <v>2</v>
-      </c>
-      <c r="E75" s="8">
+      <c r="D76" s="8">
+        <v>2</v>
+      </c>
+      <c r="E76" s="8">
         <v>4.412</v>
       </c>
-      <c r="F75" s="8">
-        <v>0</v>
-      </c>
-      <c r="G75" s="8">
+      <c r="F76" s="8">
+        <v>0</v>
+      </c>
+      <c r="G76" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="H76" s="8">
         <v>0.68</v>
       </c>
-      <c r="H75" s="8">
-        <v>0.68</v>
-      </c>
-      <c r="I75" s="8">
-        <v>0</v>
-      </c>
-      <c r="J75" s="8">
+      <c r="I76" s="8">
+        <v>0</v>
+      </c>
+      <c r="J76" s="8">
         <v>6</v>
       </c>
-      <c r="K75" s="15">
-        <v>1.376217</v>
-      </c>
-    </row>
-    <row r="76" s="4" customFormat="1" spans="1:11">
-      <c r="A76" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C76" s="8">
-        <v>3.04</v>
-      </c>
-      <c r="D76" s="8">
-        <v>3</v>
-      </c>
-      <c r="E76" s="8">
-        <v>2.703</v>
-      </c>
-      <c r="F76" s="8">
-        <v>1</v>
-      </c>
-      <c r="G76" s="8">
-        <v>1.65</v>
-      </c>
-      <c r="H76" s="8">
-        <v>0.74</v>
-      </c>
-      <c r="I76" s="8">
-        <v>0</v>
-      </c>
-      <c r="J76" s="8">
-        <v>10</v>
-      </c>
       <c r="K76" s="15">
-        <v>1.189663</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11">
+        <v>1.390089</v>
+      </c>
+    </row>
+    <row r="77" s="4" customFormat="1" spans="1:11">
       <c r="A77" s="8" t="s">
         <v>31</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C77" s="8">
+        <v>3.04</v>
+      </c>
+      <c r="D77" s="8">
+        <v>2</v>
+      </c>
+      <c r="E77" s="8">
+        <v>3.071</v>
+      </c>
+      <c r="F77" s="8">
+        <v>1</v>
+      </c>
+      <c r="G77" s="8">
+        <v>0.977</v>
+      </c>
+      <c r="H77" s="8">
+        <v>0.977</v>
+      </c>
+      <c r="I77" s="8">
+        <v>14</v>
+      </c>
+      <c r="J77" s="8">
+        <v>0</v>
+      </c>
+      <c r="K77" s="15">
+        <v>1.79015</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C78" s="8">
         <v>3.44</v>
       </c>
-      <c r="D77" s="8">
-        <v>2</v>
-      </c>
-      <c r="E77" s="8">
-        <v>4.412</v>
-      </c>
-      <c r="F77" s="8">
-        <v>0</v>
-      </c>
-      <c r="G77" s="8">
-        <v>2.2</v>
-      </c>
-      <c r="H77" s="8">
-        <v>0.68</v>
-      </c>
-      <c r="I77" s="8">
-        <v>0</v>
-      </c>
-      <c r="J77" s="8">
-        <v>6</v>
-      </c>
-      <c r="K77" s="15">
-        <v>1.390089</v>
-      </c>
-    </row>
-    <row r="78" s="4" customFormat="1" spans="1:11">
-      <c r="A78" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" s="8">
-        <v>3.04</v>
-      </c>
       <c r="D78" s="8">
         <v>2</v>
       </c>
       <c r="E78" s="8">
-        <v>3.071</v>
+        <v>4.688</v>
       </c>
       <c r="F78" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="8">
-        <v>0.977</v>
+        <v>1.63</v>
       </c>
       <c r="H78" s="8">
-        <v>0.977</v>
+        <v>0.64</v>
       </c>
       <c r="I78" s="8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J78" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K78" s="15">
-        <v>1.79015</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11">
+        <v>1.383423</v>
+      </c>
+    </row>
+    <row r="79" s="4" customFormat="1" spans="1:11">
       <c r="A79" s="8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C79" s="8">
         <v>3.44</v>
@@ -4131,86 +4131,86 @@
         <v>2</v>
       </c>
       <c r="E79" s="8">
-        <v>4.688</v>
+        <v>4.878</v>
       </c>
       <c r="F79" s="8">
         <v>0</v>
       </c>
       <c r="G79" s="8">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="H79" s="8">
-        <v>0.64</v>
+        <v>0.615</v>
       </c>
       <c r="I79" s="8">
         <v>0</v>
       </c>
       <c r="J79" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K79" s="15">
-        <v>1.383423</v>
+        <v>1.377868</v>
       </c>
     </row>
     <row r="80" s="4" customFormat="1" spans="1:11">
       <c r="A80" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C80" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D80" s="8">
         <v>2</v>
       </c>
       <c r="E80" s="8">
-        <v>4.878</v>
+        <v>2.956</v>
       </c>
       <c r="F80" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" s="8">
-        <v>1.66</v>
+        <v>1.015</v>
       </c>
       <c r="H80" s="8">
-        <v>0.615</v>
+        <v>1.015</v>
       </c>
       <c r="I80" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J80" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K80" s="15">
-        <v>1.377868</v>
+        <v>1.779418</v>
       </c>
     </row>
     <row r="81" s="4" customFormat="1" spans="1:11">
       <c r="A81" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C81" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D81" s="8">
         <v>2</v>
       </c>
       <c r="E81" s="8">
-        <v>2.956</v>
+        <v>2.799</v>
       </c>
       <c r="F81" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" s="8">
-        <v>1.015</v>
+        <v>1.23</v>
       </c>
       <c r="H81" s="8">
-        <v>1.015</v>
+        <v>1.072</v>
       </c>
       <c r="I81" s="8">
         <v>10</v>
@@ -4219,15 +4219,15 @@
         <v>0</v>
       </c>
       <c r="K81" s="15">
-        <v>1.779418</v>
+        <v>1.975642</v>
       </c>
     </row>
     <row r="82" s="4" customFormat="1" spans="1:11">
       <c r="A82" s="8" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C82" s="8">
         <v>3.44</v>
@@ -4236,33 +4236,33 @@
         <v>2</v>
       </c>
       <c r="E82" s="8">
-        <v>2.799</v>
+        <v>2.71</v>
       </c>
       <c r="F82" s="8">
         <v>0</v>
       </c>
       <c r="G82" s="8">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="H82" s="8">
-        <v>1.072</v>
+        <v>1.107</v>
       </c>
       <c r="I82" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J82" s="8">
         <v>0</v>
       </c>
       <c r="K82" s="15">
-        <v>1.975642</v>
+        <v>1.97544</v>
       </c>
     </row>
     <row r="83" s="4" customFormat="1" spans="1:11">
       <c r="A83" s="8" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C83" s="8">
         <v>3.44</v>
@@ -4271,7 +4271,7 @@
         <v>2</v>
       </c>
       <c r="E83" s="8">
-        <v>2.71</v>
+        <v>2.679</v>
       </c>
       <c r="F83" s="8">
         <v>0</v>
@@ -4280,121 +4280,121 @@
         <v>1.2</v>
       </c>
       <c r="H83" s="8">
-        <v>1.107</v>
+        <v>1.12</v>
       </c>
       <c r="I83" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J83" s="8">
         <v>0</v>
       </c>
       <c r="K83" s="15">
-        <v>1.97544</v>
-      </c>
-    </row>
-    <row r="84" s="4" customFormat="1" spans="1:11">
+        <v>1.741647</v>
+      </c>
+    </row>
+    <row r="84" s="5" customFormat="1" spans="1:11">
       <c r="A84" s="8" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C84" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D84" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E84" s="8">
-        <v>2.679</v>
+        <v>1.695</v>
       </c>
       <c r="F84" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" s="8">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="H84" s="8">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="I84" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J84" s="8">
         <v>0</v>
       </c>
       <c r="K84" s="15">
-        <v>1.741647</v>
-      </c>
-    </row>
-    <row r="85" s="5" customFormat="1" spans="1:11">
+        <v>1.871805</v>
+      </c>
+    </row>
+    <row r="85" s="4" customFormat="1" spans="1:11">
       <c r="A85" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C85" s="8">
         <v>3.04</v>
       </c>
       <c r="D85" s="8">
+        <v>2</v>
+      </c>
+      <c r="E85" s="8">
+        <v>2.705</v>
+      </c>
+      <c r="F85" s="8">
+        <v>1</v>
+      </c>
+      <c r="G85" s="8">
+        <v>1.109</v>
+      </c>
+      <c r="H85" s="8">
+        <v>1.109</v>
+      </c>
+      <c r="I85" s="8">
         <v>3</v>
       </c>
-      <c r="E85" s="8">
-        <v>1.695</v>
-      </c>
-      <c r="F85" s="8">
-        <v>1</v>
-      </c>
-      <c r="G85" s="8">
-        <v>1</v>
-      </c>
-      <c r="H85" s="8">
-        <v>1.18</v>
-      </c>
-      <c r="I85" s="8">
-        <v>0</v>
-      </c>
       <c r="J85" s="8">
         <v>0</v>
       </c>
       <c r="K85" s="15">
-        <v>1.871805</v>
+        <v>1.770991</v>
       </c>
     </row>
     <row r="86" s="4" customFormat="1" spans="1:11">
       <c r="A86" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C86" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D86" s="8">
         <v>2</v>
       </c>
       <c r="E86" s="8">
-        <v>2.705</v>
+        <v>2.852</v>
       </c>
       <c r="F86" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" s="8">
-        <v>1.109</v>
+        <v>1.25</v>
       </c>
       <c r="H86" s="8">
-        <v>1.109</v>
+        <v>1.052</v>
       </c>
       <c r="I86" s="8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J86" s="8">
         <v>0</v>
       </c>
       <c r="K86" s="15">
-        <v>1.770991</v>
+        <v>1.971139</v>
       </c>
     </row>
     <row r="87" s="4" customFormat="1" spans="1:11">
@@ -4402,34 +4402,34 @@
         <v>47</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C87" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D87" s="8">
         <v>2</v>
       </c>
       <c r="E87" s="8">
-        <v>2.852</v>
+        <v>4.348</v>
       </c>
       <c r="F87" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" s="8">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="H87" s="8">
-        <v>1.052</v>
+        <v>0.69</v>
       </c>
       <c r="I87" s="8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J87" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K87" s="15">
-        <v>1.971139</v>
+        <v>1.372387</v>
       </c>
     </row>
     <row r="88" s="4" customFormat="1" spans="1:11">
@@ -4437,112 +4437,112 @@
         <v>48</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C88" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D88" s="8">
         <v>2</v>
       </c>
       <c r="E88" s="8">
-        <v>4.348</v>
+        <v>2.545</v>
       </c>
       <c r="F88" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" s="8">
-        <v>2.16</v>
+        <v>1.13</v>
       </c>
       <c r="H88" s="8">
-        <v>0.69</v>
+        <v>1.179</v>
       </c>
       <c r="I88" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J88" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K88" s="15">
-        <v>1.372387</v>
+        <v>1.960982</v>
       </c>
     </row>
     <row r="89" s="4" customFormat="1" spans="1:11">
       <c r="A89" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C89" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D89" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E89" s="8">
-        <v>2.545</v>
+        <v>3.75</v>
       </c>
       <c r="F89" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" s="8">
-        <v>1.13</v>
+        <v>1.78</v>
       </c>
       <c r="H89" s="8">
-        <v>1.179</v>
+        <v>0.8</v>
       </c>
       <c r="I89" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J89" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K89" s="15">
-        <v>1.960982</v>
+        <v>1.254365</v>
       </c>
     </row>
     <row r="90" s="4" customFormat="1" spans="1:11">
       <c r="A90" s="8" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C90" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D90" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E90" s="8">
-        <v>3.75</v>
+        <v>3.509</v>
       </c>
       <c r="F90" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" s="8">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="H90" s="8">
-        <v>0.8</v>
+        <v>0.57</v>
       </c>
       <c r="I90" s="8">
         <v>0</v>
       </c>
       <c r="J90" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K90" s="15">
-        <v>1.254365</v>
+        <v>0.954261</v>
       </c>
     </row>
     <row r="91" s="4" customFormat="1" spans="1:11">
       <c r="A91" s="8" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C91" s="8">
         <v>3.44</v>
@@ -4551,170 +4551,170 @@
         <v>2</v>
       </c>
       <c r="E91" s="8">
-        <v>3.509</v>
+        <v>4.348</v>
       </c>
       <c r="F91" s="8">
         <v>0</v>
       </c>
       <c r="G91" s="8">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="H91" s="8">
-        <v>0.57</v>
+        <v>0.69</v>
       </c>
       <c r="I91" s="8">
         <v>0</v>
       </c>
       <c r="J91" s="8">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K91" s="15">
-        <v>0.954261</v>
+        <v>1.348408</v>
       </c>
     </row>
     <row r="92" s="4" customFormat="1" spans="1:11">
       <c r="A92" s="8" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C92" s="8">
+        <v>3.04</v>
+      </c>
+      <c r="D92" s="8">
+        <v>2</v>
+      </c>
+      <c r="E92" s="8">
+        <v>4.478</v>
+      </c>
+      <c r="F92" s="8">
+        <v>1</v>
+      </c>
+      <c r="G92" s="8">
+        <v>1.54</v>
+      </c>
+      <c r="H92" s="8">
+        <v>0.67</v>
+      </c>
+      <c r="I92" s="8">
+        <v>0</v>
+      </c>
+      <c r="J92" s="8">
+        <v>1</v>
+      </c>
+      <c r="K92" s="15">
+        <v>1.34941</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" s="8">
+        <v>3.04</v>
+      </c>
+      <c r="D93" s="8">
+        <v>3</v>
+      </c>
+      <c r="E93" s="8">
+        <v>2.77</v>
+      </c>
+      <c r="F93" s="8">
+        <v>1</v>
+      </c>
+      <c r="G93" s="8">
+        <v>1.22</v>
+      </c>
+      <c r="H93" s="8">
+        <v>1.083</v>
+      </c>
+      <c r="I93" s="8">
+        <v>9</v>
+      </c>
+      <c r="J93" s="8">
+        <v>0</v>
+      </c>
+      <c r="K93" s="15">
+        <v>1.846306</v>
+      </c>
+    </row>
+    <row r="94" s="4" customFormat="1" spans="1:11">
+      <c r="A94" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C94" s="8">
         <v>3.44</v>
       </c>
-      <c r="D92" s="8">
-        <v>2</v>
-      </c>
-      <c r="E92" s="8">
-        <v>4.348</v>
-      </c>
-      <c r="F92" s="8">
-        <v>0</v>
-      </c>
-      <c r="G92" s="8">
-        <v>2.16</v>
-      </c>
-      <c r="H92" s="8">
-        <v>0.69</v>
-      </c>
-      <c r="I92" s="8">
-        <v>0</v>
-      </c>
-      <c r="J92" s="8">
-        <v>3</v>
-      </c>
-      <c r="K92" s="15">
-        <v>1.348408</v>
-      </c>
-    </row>
-    <row r="93" s="4" customFormat="1" spans="1:11">
-      <c r="A93" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B93" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" s="8">
-        <v>3.04</v>
-      </c>
-      <c r="D93" s="8">
-        <v>2</v>
-      </c>
-      <c r="E93" s="8">
-        <v>4.478</v>
-      </c>
-      <c r="F93" s="8">
-        <v>1</v>
-      </c>
-      <c r="G93" s="8">
-        <v>1.54</v>
-      </c>
-      <c r="H93" s="8">
-        <v>0.67</v>
-      </c>
-      <c r="I93" s="8">
-        <v>0</v>
-      </c>
-      <c r="J93" s="8">
-        <v>1</v>
-      </c>
-      <c r="K93" s="15">
-        <v>1.34941</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11">
-      <c r="A94" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B94" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C94" s="8">
-        <v>3.04</v>
-      </c>
       <c r="D94" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E94" s="8">
-        <v>2.77</v>
+        <v>2.41</v>
       </c>
       <c r="F94" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" s="8">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="H94" s="8">
-        <v>1.083</v>
+        <v>0.83</v>
       </c>
       <c r="I94" s="8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J94" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K94" s="15">
-        <v>1.846306</v>
+        <v>1.337713</v>
       </c>
     </row>
     <row r="95" s="4" customFormat="1" spans="1:11">
       <c r="A95" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C95" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D95" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E95" s="8">
-        <v>2.41</v>
+        <v>3.279</v>
       </c>
       <c r="F95" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" s="8">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="H95" s="8">
-        <v>0.83</v>
+        <v>0.61</v>
       </c>
       <c r="I95" s="8">
         <v>0</v>
       </c>
       <c r="J95" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K95" s="15">
-        <v>1.337713</v>
+        <v>1.331687</v>
       </c>
     </row>
     <row r="96" s="4" customFormat="1" spans="1:11">
       <c r="A96" s="8" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="B96" s="8" t="s">
         <v>13</v>
@@ -4726,30 +4726,30 @@
         <v>3</v>
       </c>
       <c r="E96" s="8">
-        <v>3.279</v>
+        <v>3.125</v>
       </c>
       <c r="F96" s="8">
         <v>1</v>
       </c>
       <c r="G96" s="8">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="H96" s="8">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="I96" s="8">
         <v>0</v>
       </c>
       <c r="J96" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K96" s="15">
-        <v>1.331687</v>
+        <v>0.920677</v>
       </c>
     </row>
     <row r="97" s="4" customFormat="1" spans="1:11">
       <c r="A97" s="8" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B97" s="8" t="s">
         <v>13</v>
@@ -4761,7 +4761,7 @@
         <v>3</v>
       </c>
       <c r="E97" s="8">
-        <v>3.125</v>
+        <v>2.941</v>
       </c>
       <c r="F97" s="8">
         <v>1</v>
@@ -4770,21 +4770,21 @@
         <v>2.2</v>
       </c>
       <c r="H97" s="8">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="I97" s="8">
         <v>0</v>
       </c>
       <c r="J97" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K97" s="15">
-        <v>0.920677</v>
-      </c>
-    </row>
-    <row r="98" s="4" customFormat="1" spans="1:11">
+        <v>1.310791</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
       <c r="A98" s="8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B98" s="8" t="s">
         <v>13</v>
@@ -4796,103 +4796,103 @@
         <v>3</v>
       </c>
       <c r="E98" s="8">
-        <v>2.941</v>
+        <v>2.508</v>
       </c>
       <c r="F98" s="8">
         <v>1</v>
       </c>
       <c r="G98" s="8">
-        <v>2.2</v>
+        <v>1.12</v>
       </c>
       <c r="H98" s="8">
-        <v>0.68</v>
+        <v>1.196</v>
       </c>
       <c r="I98" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K98" s="15">
-        <v>1.310791</v>
+        <v>1.854005</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="8" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C99" s="8">
         <v>3.04</v>
       </c>
       <c r="D99" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E99" s="8">
-        <v>2.508</v>
+        <v>3.509</v>
       </c>
       <c r="F99" s="8">
         <v>1</v>
       </c>
       <c r="G99" s="8">
-        <v>1.12</v>
+        <v>0.57</v>
       </c>
       <c r="H99" s="8">
-        <v>1.196</v>
+        <v>0.57</v>
       </c>
       <c r="I99" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" s="8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K99" s="15">
-        <v>1.854005</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11">
+        <v>0.889082</v>
+      </c>
+    </row>
+    <row r="100" s="4" customFormat="1" spans="1:11">
       <c r="A100" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C100" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D100" s="8">
         <v>2</v>
       </c>
       <c r="E100" s="8">
-        <v>3.509</v>
+        <v>2.105</v>
       </c>
       <c r="F100" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" s="8">
-        <v>0.57</v>
+        <v>0.95</v>
       </c>
       <c r="H100" s="8">
-        <v>0.57</v>
+        <v>0.95</v>
       </c>
       <c r="I100" s="8">
         <v>0</v>
       </c>
       <c r="J100" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K100" s="15">
-        <v>0.889082</v>
-      </c>
-    </row>
-    <row r="101" s="4" customFormat="1" spans="1:11">
+        <v>1.243605</v>
+      </c>
+    </row>
+    <row r="101" s="6" customFormat="1" spans="1:11">
       <c r="A101" s="8" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C101" s="8">
         <v>3.44</v>
@@ -4901,51 +4901,51 @@
         <v>2</v>
       </c>
       <c r="E101" s="8">
-        <v>2.105</v>
+        <v>3.125</v>
       </c>
       <c r="F101" s="8">
         <v>0</v>
       </c>
       <c r="G101" s="8">
-        <v>0.95</v>
+        <v>2.2</v>
       </c>
       <c r="H101" s="8">
-        <v>0.95</v>
+        <v>0.64</v>
       </c>
       <c r="I101" s="8">
         <v>0</v>
       </c>
       <c r="J101" s="8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K101" s="15">
-        <v>1.243605</v>
+        <v>0.877937</v>
       </c>
     </row>
     <row r="102" s="6" customFormat="1" spans="1:11">
       <c r="A102" s="8" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C102" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D102" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E102" s="8">
-        <v>3.125</v>
+        <v>2.899</v>
       </c>
       <c r="F102" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" s="8">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="H102" s="8">
-        <v>0.64</v>
+        <v>0.69</v>
       </c>
       <c r="I102" s="8">
         <v>0</v>
@@ -4954,12 +4954,12 @@
         <v>8</v>
       </c>
       <c r="K102" s="15">
-        <v>0.877937</v>
+        <v>1.275855</v>
       </c>
     </row>
     <row r="103" s="6" customFormat="1" spans="1:11">
       <c r="A103" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B103" s="8" t="s">
         <v>13</v>
@@ -4971,30 +4971,30 @@
         <v>3</v>
       </c>
       <c r="E103" s="8">
-        <v>2.899</v>
+        <v>4.878</v>
       </c>
       <c r="F103" s="8">
         <v>1</v>
       </c>
       <c r="G103" s="8">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="H103" s="8">
-        <v>0.69</v>
+        <v>0.615</v>
       </c>
       <c r="I103" s="8">
         <v>0</v>
       </c>
       <c r="J103" s="8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K103" s="15">
-        <v>1.275855</v>
+        <v>1.25553</v>
       </c>
     </row>
     <row r="104" s="6" customFormat="1" spans="1:11">
       <c r="A104" s="8" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>13</v>
@@ -5006,30 +5006,30 @@
         <v>3</v>
       </c>
       <c r="E104" s="8">
-        <v>4.878</v>
+        <v>2.825</v>
       </c>
       <c r="F104" s="8">
         <v>1</v>
       </c>
       <c r="G104" s="8">
-        <v>1.66</v>
+        <v>1.24</v>
       </c>
       <c r="H104" s="8">
-        <v>0.615</v>
+        <v>1.062</v>
       </c>
       <c r="I104" s="8">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J104" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K104" s="15">
-        <v>1.25553</v>
+        <v>1.853008</v>
       </c>
     </row>
     <row r="105" s="6" customFormat="1" spans="1:11">
       <c r="A105" s="8" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B105" s="8" t="s">
         <v>13</v>
@@ -5041,240 +5041,240 @@
         <v>3</v>
       </c>
       <c r="E105" s="8">
-        <v>2.825</v>
+        <v>2.532</v>
       </c>
       <c r="F105" s="8">
         <v>1</v>
       </c>
       <c r="G105" s="8">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="H105" s="8">
-        <v>1.062</v>
+        <v>0.64</v>
       </c>
       <c r="I105" s="8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J105" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K105" s="15">
-        <v>1.853008</v>
-      </c>
-    </row>
-    <row r="106" s="6" customFormat="1" spans="1:11">
+        <v>1.2604</v>
+      </c>
+    </row>
+    <row r="106" s="7" customFormat="1" spans="1:11">
       <c r="A106" s="8" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C106" s="8">
         <v>3.04</v>
       </c>
       <c r="D106" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E106" s="8">
-        <v>2.532</v>
+        <v>2.941</v>
       </c>
       <c r="F106" s="8">
         <v>1</v>
       </c>
       <c r="G106" s="8">
-        <v>1.63</v>
+        <v>0.68</v>
       </c>
       <c r="H106" s="8">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="I106" s="8">
         <v>0</v>
       </c>
       <c r="J106" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K106" s="15">
-        <v>1.2604</v>
+        <v>1.208362</v>
       </c>
     </row>
     <row r="107" s="7" customFormat="1" spans="1:11">
       <c r="A107" s="8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C107" s="8">
         <v>3.04</v>
       </c>
       <c r="D107" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E107" s="8">
-        <v>2.941</v>
+        <v>2.799</v>
       </c>
       <c r="F107" s="8">
         <v>1</v>
       </c>
       <c r="G107" s="8">
-        <v>0.68</v>
+        <v>1.23</v>
       </c>
       <c r="H107" s="8">
-        <v>0.68</v>
+        <v>1.072</v>
       </c>
       <c r="I107" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J107" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K107" s="15">
-        <v>1.208362</v>
+        <v>1.843025</v>
       </c>
     </row>
     <row r="108" s="7" customFormat="1" spans="1:11">
       <c r="A108" s="8" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C108" s="8">
-        <v>3.04</v>
+        <v>3.44</v>
       </c>
       <c r="D108" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E108" s="8">
-        <v>2.799</v>
+        <v>2.77</v>
       </c>
       <c r="F108" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" s="8">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="H108" s="8">
-        <v>1.072</v>
+        <v>1.083</v>
       </c>
       <c r="I108" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J108" s="8">
         <v>0</v>
       </c>
       <c r="K108" s="15">
-        <v>1.843025</v>
+        <v>1.807171</v>
       </c>
     </row>
     <row r="109" s="7" customFormat="1" spans="1:11">
       <c r="A109" s="8" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C109" s="8">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="D109" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E109" s="8">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="F109" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109" s="8">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="H109" s="8">
-        <v>1.083</v>
+        <v>1.163</v>
       </c>
       <c r="I109" s="8">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J109" s="8">
         <v>0</v>
       </c>
       <c r="K109" s="15">
-        <v>1.807171</v>
+        <v>1.838206</v>
       </c>
     </row>
     <row r="110" s="7" customFormat="1" spans="1:11">
       <c r="A110" s="8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B110" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C110" s="8">
+        <v>3.04</v>
+      </c>
+      <c r="D110" s="8">
+        <v>2</v>
+      </c>
+      <c r="E110" s="8">
+        <v>3.125</v>
+      </c>
+      <c r="F110" s="8">
+        <v>1</v>
+      </c>
+      <c r="G110" s="8">
+        <v>0.64</v>
+      </c>
+      <c r="H110" s="8">
+        <v>0.64</v>
+      </c>
+      <c r="I110" s="8">
+        <v>0</v>
+      </c>
+      <c r="J110" s="8">
+        <v>8</v>
+      </c>
+      <c r="K110" s="15">
+        <v>0.824934</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B111" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C110" s="8">
-        <v>3.04</v>
-      </c>
-      <c r="D110" s="8">
+      <c r="C111" s="8">
+        <v>3.04</v>
+      </c>
+      <c r="D111" s="8">
         <v>3</v>
       </c>
-      <c r="E110" s="8">
-        <v>2.58</v>
-      </c>
-      <c r="F110" s="8">
-        <v>1</v>
-      </c>
-      <c r="G110" s="8">
-        <v>1.14</v>
-      </c>
-      <c r="H110" s="8">
-        <v>1.163</v>
-      </c>
-      <c r="I110" s="8">
-        <v>3</v>
-      </c>
-      <c r="J110" s="8">
-        <v>0</v>
-      </c>
-      <c r="K110" s="15">
-        <v>1.838206</v>
-      </c>
-    </row>
-    <row r="111" s="7" customFormat="1" spans="1:11">
-      <c r="A111" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B111" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C111" s="8">
-        <v>3.04</v>
-      </c>
-      <c r="D111" s="8">
-        <v>2</v>
-      </c>
       <c r="E111" s="8">
-        <v>3.125</v>
+        <v>2.907</v>
       </c>
       <c r="F111" s="8">
         <v>1</v>
       </c>
       <c r="G111" s="8">
-        <v>0.64</v>
+        <v>1.27</v>
       </c>
       <c r="H111" s="8">
-        <v>0.64</v>
+        <v>1.032</v>
       </c>
       <c r="I111" s="8">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J111" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K111" s="15">
-        <v>0.824934</v>
+        <v>1.844728</v>
       </c>
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="8" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B112" s="8" t="s">
         <v>13</v>
@@ -5286,30 +5286,30 @@
         <v>3</v>
       </c>
       <c r="E112" s="8">
-        <v>2.907</v>
+        <v>2.852</v>
       </c>
       <c r="F112" s="8">
         <v>1</v>
       </c>
       <c r="G112" s="8">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="H112" s="8">
-        <v>1.032</v>
+        <v>1.052</v>
       </c>
       <c r="I112" s="8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J112" s="8">
         <v>0</v>
       </c>
       <c r="K112" s="15">
-        <v>1.844728</v>
+        <v>1.833118</v>
       </c>
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="8" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="B113" s="8" t="s">
         <v>13</v>
@@ -5321,65 +5321,65 @@
         <v>3</v>
       </c>
       <c r="E113" s="8">
-        <v>2.852</v>
+        <v>3.077</v>
       </c>
       <c r="F113" s="8">
         <v>1</v>
       </c>
       <c r="G113" s="8">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="H113" s="8">
-        <v>1.052</v>
+        <v>0.65</v>
       </c>
       <c r="I113" s="8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J113" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K113" s="15">
-        <v>1.833118</v>
+        <v>1.222785</v>
       </c>
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C114" s="8">
         <v>3.04</v>
       </c>
       <c r="D114" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E114" s="8">
-        <v>3.077</v>
+        <v>3.279</v>
       </c>
       <c r="F114" s="8">
         <v>1</v>
       </c>
       <c r="G114" s="8">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="H114" s="8">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="I114" s="8">
         <v>0</v>
       </c>
       <c r="J114" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K114" s="15">
-        <v>1.222785</v>
+        <v>1.221956</v>
       </c>
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B115" s="8" t="s">
         <v>19</v>
@@ -5391,65 +5391,65 @@
         <v>2</v>
       </c>
       <c r="E115" s="8">
-        <v>3.279</v>
+        <v>2.899</v>
       </c>
       <c r="F115" s="8">
         <v>1</v>
       </c>
       <c r="G115" s="8">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="H115" s="8">
-        <v>0.61</v>
+        <v>0.69</v>
       </c>
       <c r="I115" s="8">
         <v>0</v>
       </c>
       <c r="J115" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K115" s="15">
-        <v>1.221956</v>
+        <v>1.216355</v>
       </c>
     </row>
     <row r="116" spans="1:11">
       <c r="A116" s="8" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C116" s="8">
         <v>3.04</v>
       </c>
       <c r="D116" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E116" s="8">
-        <v>2.899</v>
+        <v>2.545</v>
       </c>
       <c r="F116" s="8">
         <v>1</v>
       </c>
       <c r="G116" s="8">
-        <v>1.91</v>
+        <v>1.13</v>
       </c>
       <c r="H116" s="8">
-        <v>0.69</v>
+        <v>1.179</v>
       </c>
       <c r="I116" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J116" s="8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K116" s="15">
-        <v>1.216355</v>
+        <v>1.8034</v>
       </c>
     </row>
     <row r="117" spans="1:11">
       <c r="A117" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B117" s="8" t="s">
         <v>13</v>
@@ -5461,100 +5461,100 @@
         <v>3</v>
       </c>
       <c r="E117" s="8">
-        <v>2.545</v>
+        <v>2.71</v>
       </c>
       <c r="F117" s="8">
         <v>1</v>
       </c>
       <c r="G117" s="8">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="H117" s="8">
-        <v>1.179</v>
+        <v>1.107</v>
       </c>
       <c r="I117" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J117" s="8">
         <v>0</v>
       </c>
       <c r="K117" s="15">
-        <v>1.8034</v>
+        <v>1.810199</v>
       </c>
     </row>
     <row r="118" spans="1:11">
       <c r="A118" s="8" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C118" s="8">
         <v>3.04</v>
       </c>
       <c r="D118" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E118" s="8">
-        <v>2.71</v>
+        <v>1.786</v>
       </c>
       <c r="F118" s="8">
         <v>1</v>
       </c>
       <c r="G118" s="8">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="H118" s="8">
-        <v>1.107</v>
+        <v>1.12</v>
       </c>
       <c r="I118" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J118" s="8">
         <v>0</v>
       </c>
       <c r="K118" s="15">
-        <v>1.810199</v>
+        <v>1.503763</v>
       </c>
     </row>
     <row r="119" spans="1:11">
       <c r="A119" s="8" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C119" s="8">
         <v>3.04</v>
       </c>
       <c r="D119" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E119" s="8">
-        <v>1.786</v>
+        <v>4.348</v>
       </c>
       <c r="F119" s="8">
         <v>1</v>
       </c>
       <c r="G119" s="8">
-        <v>1</v>
+        <v>2.16</v>
       </c>
       <c r="H119" s="8">
-        <v>1.12</v>
+        <v>0.69</v>
       </c>
       <c r="I119" s="8">
         <v>0</v>
       </c>
       <c r="J119" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K119" s="15">
-        <v>1.503763</v>
+        <v>1.190333</v>
       </c>
     </row>
     <row r="120" spans="1:11">
       <c r="A120" s="8" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="B120" s="8" t="s">
         <v>13</v>
@@ -5566,30 +5566,30 @@
         <v>3</v>
       </c>
       <c r="E120" s="8">
-        <v>4.348</v>
+        <v>2.467</v>
       </c>
       <c r="F120" s="8">
         <v>1</v>
       </c>
       <c r="G120" s="8">
-        <v>2.16</v>
+        <v>1.1</v>
       </c>
       <c r="H120" s="8">
-        <v>0.69</v>
+        <v>1.216</v>
       </c>
       <c r="I120" s="8">
         <v>0</v>
       </c>
       <c r="J120" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K120" s="15">
-        <v>1.190333</v>
+        <v>1.789009</v>
       </c>
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="8" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B121" s="8" t="s">
         <v>13</v>
@@ -5601,16 +5601,16 @@
         <v>3</v>
       </c>
       <c r="E121" s="8">
-        <v>2.467</v>
+        <v>6.612</v>
       </c>
       <c r="F121" s="8">
         <v>1</v>
       </c>
       <c r="G121" s="8">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="H121" s="8">
-        <v>1.216</v>
+        <v>0.605</v>
       </c>
       <c r="I121" s="8">
         <v>0</v>
@@ -5619,47 +5619,47 @@
         <v>0</v>
       </c>
       <c r="K121" s="15">
-        <v>1.789009</v>
+        <v>1.172127</v>
       </c>
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="8" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C122" s="8">
         <v>3.04</v>
       </c>
       <c r="D122" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E122" s="8">
-        <v>6.612</v>
+        <v>3.509</v>
       </c>
       <c r="F122" s="8">
         <v>1</v>
       </c>
       <c r="G122" s="8">
-        <v>1.54</v>
+        <v>0.57</v>
       </c>
       <c r="H122" s="8">
-        <v>0.605</v>
+        <v>0.57</v>
       </c>
       <c r="I122" s="8">
         <v>0</v>
       </c>
       <c r="J122" s="8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K122" s="15">
-        <v>1.172127</v>
+        <v>0.754474</v>
       </c>
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B123" s="8" t="s">
         <v>19</v>
@@ -5671,30 +5671,30 @@
         <v>2</v>
       </c>
       <c r="E123" s="8">
-        <v>3.509</v>
+        <v>3.077</v>
       </c>
       <c r="F123" s="8">
         <v>1</v>
       </c>
       <c r="G123" s="8">
-        <v>0.57</v>
+        <v>1.88</v>
       </c>
       <c r="H123" s="8">
-        <v>0.57</v>
+        <v>0.745</v>
       </c>
       <c r="I123" s="8">
         <v>0</v>
       </c>
       <c r="J123" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K123" s="15">
-        <v>0.754474</v>
+        <v>1.166227</v>
       </c>
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="8" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B124" s="8" t="s">
         <v>19</v>
@@ -5706,30 +5706,30 @@
         <v>2</v>
       </c>
       <c r="E124" s="8">
-        <v>3.077</v>
+        <v>2.586</v>
       </c>
       <c r="F124" s="8">
         <v>1</v>
       </c>
       <c r="G124" s="8">
-        <v>1.88</v>
+        <v>1.16</v>
       </c>
       <c r="H124" s="8">
-        <v>0.745</v>
+        <v>1.16</v>
       </c>
       <c r="I124" s="8">
         <v>0</v>
       </c>
       <c r="J124" s="8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K124" s="15">
-        <v>1.166227</v>
+        <v>1.502635</v>
       </c>
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="8" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B125" s="8" t="s">
         <v>19</v>
@@ -5741,25 +5741,25 @@
         <v>2</v>
       </c>
       <c r="E125" s="8">
-        <v>2.586</v>
+        <v>3.333</v>
       </c>
       <c r="F125" s="8">
         <v>1</v>
       </c>
       <c r="G125" s="8">
-        <v>1.16</v>
+        <v>0.6</v>
       </c>
       <c r="H125" s="8">
-        <v>1.16</v>
+        <v>0.6</v>
       </c>
       <c r="I125" s="8">
         <v>0</v>
       </c>
       <c r="J125" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K125" s="15">
-        <v>1.502635</v>
+        <v>0.704694</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -5767,144 +5767,144 @@
         <v>25</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C126" s="8">
         <v>3.04</v>
       </c>
       <c r="D126" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E126" s="8">
-        <v>3.333</v>
+        <v>2.985</v>
       </c>
       <c r="F126" s="8">
         <v>1</v>
       </c>
       <c r="G126" s="8">
-        <v>0.6</v>
+        <v>1.55</v>
       </c>
       <c r="H126" s="8">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="I126" s="8">
         <v>0</v>
       </c>
       <c r="J126" s="8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K126" s="15">
-        <v>0.704694</v>
+        <v>1.136419</v>
       </c>
     </row>
     <row r="127" spans="1:11">
       <c r="A127" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C127" s="8">
         <v>3.04</v>
       </c>
       <c r="D127" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E127" s="8">
-        <v>2.985</v>
+        <v>4.412</v>
       </c>
       <c r="F127" s="8">
         <v>1</v>
       </c>
       <c r="G127" s="8">
-        <v>1.55</v>
+        <v>0.68</v>
       </c>
       <c r="H127" s="8">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="I127" s="8">
         <v>0</v>
       </c>
       <c r="J127" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K127" s="15">
-        <v>1.136419</v>
+        <v>1.122922</v>
       </c>
     </row>
     <row r="128" spans="1:11">
       <c r="A128" s="8" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C128" s="8">
         <v>3.04</v>
       </c>
       <c r="D128" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E128" s="8">
-        <v>4.412</v>
+        <v>3.077</v>
       </c>
       <c r="F128" s="8">
         <v>1</v>
       </c>
       <c r="G128" s="8">
-        <v>0.68</v>
+        <v>1.9</v>
       </c>
       <c r="H128" s="8">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="I128" s="8">
         <v>0</v>
       </c>
       <c r="J128" s="8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K128" s="15">
-        <v>1.122922</v>
+        <v>0.920467</v>
       </c>
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="8" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C129" s="8">
         <v>3.04</v>
       </c>
       <c r="D129" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E129" s="8">
-        <v>3.077</v>
+        <v>2.625</v>
       </c>
       <c r="F129" s="8">
         <v>1</v>
       </c>
       <c r="G129" s="8">
-        <v>1.9</v>
+        <v>1.143</v>
       </c>
       <c r="H129" s="8">
-        <v>0.65</v>
+        <v>1.143</v>
       </c>
       <c r="I129" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J129" s="8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K129" s="15">
-        <v>0.920467</v>
+        <v>1.477847</v>
       </c>
     </row>
     <row r="130" spans="1:11">
       <c r="A130" s="8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B130" s="8" t="s">
         <v>19</v>
@@ -5916,30 +5916,30 @@
         <v>2</v>
       </c>
       <c r="E130" s="8">
-        <v>2.625</v>
+        <v>2.921</v>
       </c>
       <c r="F130" s="8">
         <v>1</v>
       </c>
       <c r="G130" s="8">
-        <v>1.143</v>
+        <v>1.027</v>
       </c>
       <c r="H130" s="8">
-        <v>1.143</v>
+        <v>1.027</v>
       </c>
       <c r="I130" s="8">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J130" s="8">
         <v>0</v>
       </c>
       <c r="K130" s="15">
-        <v>1.477847</v>
+        <v>1.495429</v>
       </c>
     </row>
     <row r="131" spans="1:11">
       <c r="A131" s="8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B131" s="8" t="s">
         <v>19</v>
@@ -5951,30 +5951,30 @@
         <v>2</v>
       </c>
       <c r="E131" s="8">
-        <v>2.921</v>
+        <v>2.988</v>
       </c>
       <c r="F131" s="8">
         <v>1</v>
       </c>
       <c r="G131" s="8">
-        <v>1.027</v>
+        <v>1.004</v>
       </c>
       <c r="H131" s="8">
-        <v>1.027</v>
+        <v>1.004</v>
       </c>
       <c r="I131" s="8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J131" s="8">
         <v>0</v>
       </c>
       <c r="K131" s="15">
-        <v>1.495429</v>
+        <v>1.505762</v>
       </c>
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="8" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B132" s="8" t="s">
         <v>19</v>
@@ -5986,30 +5986,30 @@
         <v>2</v>
       </c>
       <c r="E132" s="8">
-        <v>2.988</v>
+        <v>4.511</v>
       </c>
       <c r="F132" s="8">
         <v>1</v>
       </c>
       <c r="G132" s="8">
-        <v>1.004</v>
+        <v>0.665</v>
       </c>
       <c r="H132" s="8">
-        <v>1.004</v>
+        <v>0.665</v>
       </c>
       <c r="I132" s="8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J132" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K132" s="15">
-        <v>1.505762</v>
+        <v>1.015029</v>
       </c>
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="8" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B133" s="8" t="s">
         <v>19</v>
@@ -6021,30 +6021,30 @@
         <v>2</v>
       </c>
       <c r="E133" s="8">
-        <v>4.511</v>
+        <v>3.046</v>
       </c>
       <c r="F133" s="8">
         <v>1</v>
       </c>
       <c r="G133" s="8">
-        <v>0.665</v>
+        <v>0.985</v>
       </c>
       <c r="H133" s="8">
-        <v>0.665</v>
+        <v>0.985</v>
       </c>
       <c r="I133" s="8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J133" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K133" s="15">
-        <v>1.015029</v>
+        <v>1.479314</v>
       </c>
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="8" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B134" s="8" t="s">
         <v>19</v>
@@ -6056,30 +6056,30 @@
         <v>2</v>
       </c>
       <c r="E134" s="8">
-        <v>3.046</v>
+        <v>2.849</v>
       </c>
       <c r="F134" s="8">
         <v>1</v>
       </c>
       <c r="G134" s="8">
-        <v>0.985</v>
+        <v>1.053</v>
       </c>
       <c r="H134" s="8">
-        <v>0.985</v>
+        <v>1.053</v>
       </c>
       <c r="I134" s="8">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J134" s="8">
         <v>0</v>
       </c>
       <c r="K134" s="15">
-        <v>1.479314</v>
+        <v>1.499809</v>
       </c>
     </row>
     <row r="135" spans="1:11">
       <c r="A135" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B135" s="8" t="s">
         <v>19</v>
@@ -6091,30 +6091,30 @@
         <v>2</v>
       </c>
       <c r="E135" s="8">
-        <v>2.849</v>
+        <v>2.705</v>
       </c>
       <c r="F135" s="8">
         <v>1</v>
       </c>
       <c r="G135" s="8">
-        <v>1.053</v>
+        <v>1.109</v>
       </c>
       <c r="H135" s="8">
-        <v>1.053</v>
+        <v>1.109</v>
       </c>
       <c r="I135" s="8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J135" s="8">
         <v>0</v>
       </c>
       <c r="K135" s="15">
-        <v>1.499809</v>
+        <v>1.4841</v>
       </c>
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="8" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B136" s="8" t="s">
         <v>19</v>
@@ -6126,30 +6126,30 @@
         <v>2</v>
       </c>
       <c r="E136" s="8">
-        <v>2.705</v>
+        <v>3.071</v>
       </c>
       <c r="F136" s="8">
         <v>1</v>
       </c>
       <c r="G136" s="8">
-        <v>1.109</v>
+        <v>0.977</v>
       </c>
       <c r="H136" s="8">
-        <v>1.109</v>
+        <v>0.977</v>
       </c>
       <c r="I136" s="8">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J136" s="8">
         <v>0</v>
       </c>
       <c r="K136" s="15">
-        <v>1.4841</v>
+        <v>1.483216</v>
       </c>
     </row>
     <row r="137" spans="1:11">
       <c r="A137" s="8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B137" s="8" t="s">
         <v>19</v>
@@ -6161,30 +6161,30 @@
         <v>2</v>
       </c>
       <c r="E137" s="8">
-        <v>3.071</v>
+        <v>2.532</v>
       </c>
       <c r="F137" s="8">
         <v>1</v>
       </c>
       <c r="G137" s="8">
-        <v>0.977</v>
+        <v>1.63</v>
       </c>
       <c r="H137" s="8">
-        <v>0.977</v>
+        <v>0.79</v>
       </c>
       <c r="I137" s="8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J137" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K137" s="15">
-        <v>1.483216</v>
+        <v>1.064441</v>
       </c>
     </row>
     <row r="138" spans="1:11">
       <c r="A138" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B138" s="8" t="s">
         <v>19</v>
@@ -6196,30 +6196,30 @@
         <v>2</v>
       </c>
       <c r="E138" s="8">
-        <v>2.532</v>
+        <v>2.956</v>
       </c>
       <c r="F138" s="8">
         <v>1</v>
       </c>
       <c r="G138" s="8">
-        <v>1.63</v>
+        <v>1.015</v>
       </c>
       <c r="H138" s="8">
-        <v>0.79</v>
+        <v>1.015</v>
       </c>
       <c r="I138" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J138" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K138" s="15">
-        <v>1.064441</v>
+        <v>1.44145</v>
       </c>
     </row>
     <row r="139" spans="1:11">
       <c r="A139" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B139" s="8" t="s">
         <v>19</v>
@@ -6231,30 +6231,30 @@
         <v>2</v>
       </c>
       <c r="E139" s="8">
-        <v>2.956</v>
+        <v>4.878</v>
       </c>
       <c r="F139" s="8">
         <v>1</v>
       </c>
       <c r="G139" s="8">
-        <v>1.015</v>
+        <v>1.66</v>
       </c>
       <c r="H139" s="8">
-        <v>1.015</v>
+        <v>0.615</v>
       </c>
       <c r="I139" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J139" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K139" s="15">
-        <v>1.44145</v>
+        <v>1.029483</v>
       </c>
     </row>
     <row r="140" spans="1:11">
       <c r="A140" s="8" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B140" s="8" t="s">
         <v>19</v>
@@ -6266,16 +6266,16 @@
         <v>2</v>
       </c>
       <c r="E140" s="8">
-        <v>4.878</v>
+        <v>4.348</v>
       </c>
       <c r="F140" s="8">
         <v>1</v>
       </c>
       <c r="G140" s="8">
-        <v>1.66</v>
+        <v>2.16</v>
       </c>
       <c r="H140" s="8">
-        <v>0.615</v>
+        <v>0.69</v>
       </c>
       <c r="I140" s="8">
         <v>0</v>
@@ -6284,12 +6284,12 @@
         <v>3</v>
       </c>
       <c r="K140" s="15">
-        <v>1.029483</v>
+        <v>1.039938</v>
       </c>
     </row>
     <row r="141" spans="1:11">
       <c r="A141" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B141" s="8" t="s">
         <v>19</v>
@@ -6301,30 +6301,30 @@
         <v>2</v>
       </c>
       <c r="E141" s="8">
-        <v>4.348</v>
+        <v>2.78</v>
       </c>
       <c r="F141" s="8">
         <v>1</v>
       </c>
       <c r="G141" s="8">
-        <v>2.16</v>
+        <v>1.079</v>
       </c>
       <c r="H141" s="8">
-        <v>0.69</v>
+        <v>1.079</v>
       </c>
       <c r="I141" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J141" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K141" s="15">
-        <v>1.039938</v>
+        <v>1.39301</v>
       </c>
     </row>
     <row r="142" spans="1:11">
       <c r="A142" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B142" s="8" t="s">
         <v>19</v>
@@ -6336,30 +6336,30 @@
         <v>2</v>
       </c>
       <c r="E142" s="8">
-        <v>2.78</v>
+        <v>2.852</v>
       </c>
       <c r="F142" s="8">
         <v>1</v>
       </c>
       <c r="G142" s="8">
-        <v>1.079</v>
+        <v>0.994</v>
       </c>
       <c r="H142" s="8">
-        <v>1.079</v>
+        <v>0.994</v>
       </c>
       <c r="I142" s="8">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J142" s="8">
         <v>0</v>
       </c>
       <c r="K142" s="15">
-        <v>1.39301</v>
+        <v>1.419205</v>
       </c>
     </row>
     <row r="143" spans="1:11">
       <c r="A143" s="8" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B143" s="8" t="s">
         <v>19</v>
@@ -6371,51 +6371,51 @@
         <v>2</v>
       </c>
       <c r="E143" s="8">
-        <v>2.852</v>
+        <v>5.556</v>
       </c>
       <c r="F143" s="8">
         <v>1</v>
       </c>
       <c r="G143" s="8">
-        <v>0.994</v>
+        <v>0.72</v>
       </c>
       <c r="H143" s="8">
-        <v>0.994</v>
+        <v>0.72</v>
       </c>
       <c r="I143" s="8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J143" s="8">
         <v>0</v>
       </c>
       <c r="K143" s="15">
-        <v>1.419205</v>
+        <v>0.764731</v>
       </c>
     </row>
     <row r="144" spans="1:11">
       <c r="A144" s="8" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C144" s="8">
         <v>3.04</v>
       </c>
       <c r="D144" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E144" s="8">
-        <v>5.556</v>
+        <v>10</v>
       </c>
       <c r="F144" s="8">
         <v>1</v>
       </c>
       <c r="G144" s="8">
-        <v>0.72</v>
+        <v>2.36</v>
       </c>
       <c r="H144" s="8">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="I144" s="8">
         <v>0</v>
@@ -6424,51 +6424,16 @@
         <v>0</v>
       </c>
       <c r="K144" s="15">
-        <v>0.764731</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11">
-      <c r="A145" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B145" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C145" s="8">
-        <v>3.04</v>
-      </c>
-      <c r="D145" s="8">
-        <v>3</v>
-      </c>
-      <c r="E145" s="8">
-        <v>10</v>
-      </c>
-      <c r="F145" s="8">
-        <v>1</v>
-      </c>
-      <c r="G145" s="8">
-        <v>2.36</v>
-      </c>
-      <c r="H145" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="I145" s="8">
-        <v>0</v>
-      </c>
-      <c r="J145" s="8">
-        <v>0</v>
-      </c>
-      <c r="K145" s="15">
         <v>0.509731</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="150" spans="1:2">
+      <c r="A150" s="16"/>
+      <c r="B150" s="16"/>
+    </row>
+    <row r="151" spans="1:2">
       <c r="A151" s="16"/>
       <c r="B151" s="16"/>
-    </row>
-    <row r="152" spans="1:11">
-      <c r="A152" s="16"/>
-      <c r="B152" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
